--- a/test/excel/win/lines/files/written.xlsx
+++ b/test/excel/win/lines/files/written.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\lines-files-53320-1\out\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\lines-files-8146-1\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA668058-1153-408A-9CB4-985381B2CF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89ECD478-9D14-4C13-89C2-20D4AA0F1158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -482,12 +482,12 @@
     <col min="7" max="7" width="14" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1">
         <v>46096</v>
       </c>
@@ -498,7 +498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="1" cm="1">
         <f t="array" ref="B3">B2+1</f>
         <v>46097</v>
@@ -511,18 +511,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>46096</v>
       </c>
       <c r="D4" s="11">
         <v>1234.5</v>
       </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="12">
         <v>1234.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>46096</v>
       </c>
@@ -532,8 +533,9 @@
       <c r="F6" s="13">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G6" s="9"/>
+    </row>
+    <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>46096</v>
       </c>
@@ -541,33 +543,33 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="1" cm="1">
         <f t="array" ref="B12:B13">_xlfn.SEQUENCE(2,1,46096)</f>
         <v>46096</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>46097</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>46096</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <v>46096</v>
       </c>
